--- a/data/rolling.xlsx
+++ b/data/rolling.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\ugfit022\VOL4\MYSALES\Cubaiu-L\SALES_CONTROLLING\GIORNALIERI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{736F116B-8936-417E-B710-6BB6E5A324C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{49555135-2999-44EE-85E3-C1BAAE97BA66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21240" xr2:uid="{DB4B0AE0-21E8-4877-AD07-31589DC632AE}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{6276B37E-66FD-4E92-A48B-FA59C0CD80C5}"/>
   </bookViews>
   <sheets>
     <sheet name="REPORT" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">REPORT!$A$4:$AO$116</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">REPORT!$A$1:$AV$116</definedName>
   </definedNames>
-  <calcPr calcId="191029" concurrentManualCount="6"/>
+  <calcPr calcId="191029" concurrentManualCount="8"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -48,7 +48,7 @@
     <t>AGGIORNATO:</t>
   </si>
   <si>
-    <t>28/04/2026</t>
+    <t>30/04/2026</t>
   </si>
   <si>
     <t>Fatturato TOTALE 2024</t>
@@ -132,10 +132,10 @@
     <t>GTO Dic'26</t>
   </si>
   <si>
-    <t>MESE: Consegnato al 28/04/2026</t>
-  </si>
-  <si>
-    <t>MESE: In preparazione a magazzino al 28/04/2026</t>
+    <t>MESE: Consegnato al 30/04/2026</t>
+  </si>
+  <si>
+    <t>MESE: In preparazione a magazzino al 30/04/2026</t>
   </si>
   <si>
     <t>Da spedire nel mese di aprile 2026</t>
@@ -1177,13 +1177,13 @@
     </xf>
   </cellXfs>
   <cellStyles count="7">
-    <cellStyle name="Migliaia 2" xfId="4" xr:uid="{33E8D5A0-9900-494A-93AE-7F6A4329497F}"/>
+    <cellStyle name="Migliaia 2" xfId="4" xr:uid="{6EBB2784-882C-47AA-BA41-BD0DBB30778C}"/>
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
-    <cellStyle name="Normale 20" xfId="1" xr:uid="{2E184E89-CB38-41A6-81DC-856E09CB8121}"/>
-    <cellStyle name="Normale 21" xfId="2" xr:uid="{472EE9FA-2826-4243-A333-1B5619402555}"/>
-    <cellStyle name="Normale 22" xfId="3" xr:uid="{16B91A1B-57AE-44C8-8770-421E6CDD48D5}"/>
-    <cellStyle name="SAPDataCell" xfId="6" xr:uid="{E45A21A6-DFE2-4607-B41F-2A429BE1301A}"/>
-    <cellStyle name="SAPMemberCell" xfId="5" xr:uid="{7A24F2EA-53C3-4B55-A2DB-18F1F8B58A4B}"/>
+    <cellStyle name="Normale 20" xfId="1" xr:uid="{4F288485-45CF-49A4-BAA1-1503955F4346}"/>
+    <cellStyle name="Normale 21" xfId="2" xr:uid="{C765FF2A-1818-49BF-BF92-4BF54E32ED01}"/>
+    <cellStyle name="Normale 22" xfId="3" xr:uid="{1E4CF2C7-9FD9-4651-BDD2-2602F6321360}"/>
+    <cellStyle name="SAPDataCell" xfId="6" xr:uid="{2A900F4B-49E3-4B2B-BDAF-4CD054620FE3}"/>
+    <cellStyle name="SAPMemberCell" xfId="5" xr:uid="{DBF3A124-A9A6-4C0E-9B2C-E60BB3363AEE}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1514,52 +1514,53 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DD1AA80-B25D-432D-986A-8039B0E1D075}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF940CA3-7230-4574-93CE-C32F98188DB4}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:EG116"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.28515625" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="18.7109375" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="37.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="21" width="7.28515625" customWidth="1"/>
-    <col min="22" max="22" width="15.28515625" customWidth="1"/>
-    <col min="23" max="25" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="26" max="31" width="2.5703125" bestFit="1" customWidth="1"/>
-    <col min="32" max="34" width="2.85546875" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="21.28515625" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.33203125" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="18.6640625" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="37.21875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.21875" bestFit="1" customWidth="1"/>
+    <col min="11" max="21" width="7.21875" customWidth="1"/>
+    <col min="22" max="22" width="15.21875" customWidth="1"/>
+    <col min="23" max="24" width="7.21875" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="26" max="31" width="2.5546875" bestFit="1" customWidth="1"/>
+    <col min="32" max="34" width="2.88671875" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="21.21875" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="19.21875" bestFit="1" customWidth="1"/>
     <col min="37" max="37" width="20" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="26.140625" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="27.5703125" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="34.42578125" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="26.109375" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="27.5546875" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="34.44140625" bestFit="1" customWidth="1"/>
     <col min="43" max="43" width="28" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="40.5703125" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="2.28515625" customWidth="1"/>
-    <col min="46" max="46" width="22.42578125" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="40.5546875" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="2.33203125" customWidth="1"/>
+    <col min="46" max="46" width="22.44140625" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="22.109375" bestFit="1" customWidth="1"/>
     <col min="48" max="48" width="23" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="22.28515625" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="27.7109375" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="28.7109375" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="36.7109375" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="29.28515625" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="43.140625" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="27.6640625" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="28.6640625" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="36.6640625" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="29.33203125" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="43.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:137" ht="23.25" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:137" ht="22.8" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1577,7 +1578,7 @@
       <c r="AR1" s="2"/>
       <c r="AS1" s="2"/>
     </row>
-    <row r="2" spans="1:137" ht="15" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:137" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -1599,7 +1600,7 @@
       <c r="AR2" s="2"/>
       <c r="AS2" s="2"/>
     </row>
-    <row r="3" spans="1:137" ht="102" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:137" ht="105.6" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>285</v>
       </c>
@@ -1724,7 +1725,7 @@
       </c>
       <c r="AS3" s="14"/>
     </row>
-    <row r="4" spans="1:137" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:137" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="15" t="s">
         <v>40</v>
       </c>
@@ -1854,19 +1855,19 @@
       </c>
       <c r="AI4" s="16">
         <f>SUBTOTAL(9,AI5:AI63748)</f>
-        <v>92851.549999999988</v>
+        <v>98276.709999999992</v>
       </c>
       <c r="AJ4" s="16">
         <f>SUBTOTAL(9,AJ5:AJ63748)</f>
-        <v>1307.8800000000001</v>
+        <v>1341.66</v>
       </c>
       <c r="AK4" s="16">
         <f>SUBTOTAL(9,AK5:AK63748)</f>
-        <v>3705.9499999999989</v>
+        <v>2442.2899999999991</v>
       </c>
       <c r="AL4" s="16">
         <f>SUBTOTAL(9,AL5:AL63748)</f>
-        <v>6739.21</v>
+        <v>11504.76</v>
       </c>
       <c r="AM4" s="16">
         <f>SUBTOTAL(9,AM5:AM63748)</f>
@@ -1874,11 +1875,11 @@
       </c>
       <c r="AN4" s="16">
         <f>SUBTOTAL(9,AN5:AN63748)</f>
-        <v>97865.379999999976</v>
+        <v>102060.65999999997</v>
       </c>
       <c r="AO4" s="16">
         <f>SUBTOTAL(9,AO5:AO63748)</f>
-        <v>-6953.19</v>
+        <v>-2757.9100000000035</v>
       </c>
       <c r="AP4" s="16">
         <f>SUBTOTAL(9,AP5:AP63748)</f>
@@ -1886,11 +1887,11 @@
       </c>
       <c r="AQ4" s="16">
         <f>SUBTOTAL(9,AQ5:AQ63748)</f>
-        <v>450759.88000000006</v>
+        <v>454955.16000000003</v>
       </c>
       <c r="AR4" s="16">
         <f>SUBTOTAL(9,AR5:AR63748)</f>
-        <v>15670.859999999997</v>
+        <v>19866.139999999996</v>
       </c>
       <c r="AS4" s="16"/>
       <c r="AT4" s="17" t="s">
@@ -1994,7 +1995,7 @@
       <c r="EF4" s="5"/>
       <c r="EG4" s="5"/>
     </row>
-    <row r="5" spans="1:137" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:137" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="20" t="s">
         <v>49</v>
       </c>
@@ -2081,7 +2082,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="6" spans="1:137" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:137" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="20" t="s">
         <v>49</v>
       </c>
@@ -2174,7 +2175,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="7" spans="1:137" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:137" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="20" t="s">
         <v>49</v>
       </c>
@@ -2279,7 +2280,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="8" spans="1:137" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:137" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="20" t="s">
         <v>49</v>
       </c>
@@ -2365,10 +2366,10 @@
       <c r="AG8" s="21"/>
       <c r="AH8" s="21"/>
       <c r="AI8" s="21">
-        <v>788.25</v>
+        <v>1171.05</v>
       </c>
       <c r="AJ8" s="21">
-        <v>382.8</v>
+        <v>0</v>
       </c>
       <c r="AK8" s="21">
         <v>0</v>
@@ -2406,7 +2407,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="9" spans="1:137" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:137" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="20" t="s">
         <v>49</v>
       </c>
@@ -2507,7 +2508,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="10" spans="1:137" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:137" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="20" t="s">
         <v>49</v>
       </c>
@@ -2596,7 +2597,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="11" spans="1:137" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:137" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="20" t="s">
         <v>49</v>
       </c>
@@ -2683,7 +2684,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="12" spans="1:137" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:137" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="20" t="s">
         <v>49</v>
       </c>
@@ -2786,7 +2787,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="13" spans="1:137" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:137" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="20" t="s">
         <v>49</v>
       </c>
@@ -2885,7 +2886,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="14" spans="1:137" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:137" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="20" t="s">
         <v>49</v>
       </c>
@@ -2994,7 +2995,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="15" spans="1:137" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:137" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="20" t="s">
         <v>49</v>
       </c>
@@ -3076,13 +3077,13 @@
       <c r="AG15" s="21"/>
       <c r="AH15" s="21"/>
       <c r="AI15" s="21">
-        <v>628.03</v>
+        <v>718.4</v>
       </c>
       <c r="AJ15" s="21">
         <v>0</v>
       </c>
       <c r="AK15" s="21">
-        <v>90.37</v>
+        <v>0</v>
       </c>
       <c r="AL15" s="21"/>
       <c r="AM15" s="21">
@@ -3117,7 +3118,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="16" spans="1:137" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:137" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="20" t="s">
         <v>49</v>
       </c>
@@ -3212,7 +3213,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="17" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="20" t="s">
         <v>49</v>
       </c>
@@ -3297,7 +3298,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="18" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="20" t="s">
         <v>49</v>
       </c>
@@ -3386,31 +3387,31 @@
         <v>5306.62</v>
       </c>
       <c r="AJ18" s="21">
-        <v>0</v>
+        <v>185.4</v>
       </c>
       <c r="AK18" s="21">
         <v>0</v>
       </c>
       <c r="AL18" s="21">
-        <v>779.81</v>
+        <v>594.41</v>
       </c>
       <c r="AM18" s="21">
         <v>5796.17</v>
       </c>
       <c r="AN18" s="21">
-        <v>5306.62</v>
+        <v>5492.02</v>
       </c>
       <c r="AO18" s="21">
-        <v>-489.55</v>
+        <v>-304.14999999999998</v>
       </c>
       <c r="AP18" s="22">
         <v>21500.95</v>
       </c>
       <c r="AQ18" s="21">
-        <v>27877.56</v>
+        <v>28062.959999999999</v>
       </c>
       <c r="AR18" s="23">
-        <v>6376.61</v>
+        <v>6562.01</v>
       </c>
       <c r="AS18" s="24"/>
       <c r="AT18" s="19" t="s">
@@ -3426,7 +3427,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="19" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="20" t="s">
         <v>49</v>
       </c>
@@ -3549,7 +3550,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="20" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="20" t="s">
         <v>49</v>
       </c>
@@ -3662,7 +3663,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="21" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="20" t="s">
         <v>49</v>
       </c>
@@ -3763,7 +3764,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="22" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="20" t="s">
         <v>49</v>
       </c>
@@ -3870,7 +3871,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="23" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="20" t="s">
         <v>49</v>
       </c>
@@ -3981,7 +3982,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="24" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="20" t="s">
         <v>49</v>
       </c>
@@ -4072,7 +4073,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="25" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="20" t="s">
         <v>49</v>
       </c>
@@ -4189,7 +4190,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="26" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="20" t="s">
         <v>49</v>
       </c>
@@ -4286,7 +4287,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="27" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="20" t="s">
         <v>49</v>
       </c>
@@ -4413,7 +4414,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="28" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="20" t="s">
         <v>49</v>
       </c>
@@ -4534,7 +4535,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="29" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="20" t="s">
         <v>49</v>
       </c>
@@ -4641,7 +4642,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="30" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="20" t="s">
         <v>49</v>
       </c>
@@ -4764,7 +4765,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="31" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="20" t="s">
         <v>49</v>
       </c>
@@ -4857,7 +4858,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="32" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="20" t="s">
         <v>49</v>
       </c>
@@ -4952,7 +4953,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="33" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="20" t="s">
         <v>49</v>
       </c>
@@ -5049,7 +5050,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="34" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="20" t="s">
         <v>49</v>
       </c>
@@ -5176,7 +5177,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="35" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="20" t="s">
         <v>49</v>
       </c>
@@ -5275,7 +5276,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="36" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="20" t="s">
         <v>49</v>
       </c>
@@ -5362,7 +5363,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="37" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="20" t="s">
         <v>49</v>
       </c>
@@ -5461,7 +5462,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="38" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="20" t="s">
         <v>49</v>
       </c>
@@ -5544,12 +5545,14 @@
       <c r="AF38" s="21"/>
       <c r="AG38" s="21"/>
       <c r="AH38" s="21"/>
-      <c r="AI38" s="21"/>
+      <c r="AI38" s="21">
+        <v>964.91</v>
+      </c>
       <c r="AJ38" s="21">
         <v>0</v>
       </c>
       <c r="AK38" s="21">
-        <v>472.3</v>
+        <v>0</v>
       </c>
       <c r="AL38" s="21">
         <v>0</v>
@@ -5558,19 +5561,19 @@
         <v>1898.84</v>
       </c>
       <c r="AN38" s="21">
-        <v>472.3</v>
+        <v>964.91</v>
       </c>
       <c r="AO38" s="21">
-        <v>-1426.54</v>
+        <v>-933.93</v>
       </c>
       <c r="AP38" s="22">
         <v>8344.57</v>
       </c>
       <c r="AQ38" s="21">
-        <v>5901.1</v>
+        <v>6393.71</v>
       </c>
       <c r="AR38" s="23">
-        <v>-2443.4699999999998</v>
+        <v>-1950.86</v>
       </c>
       <c r="AS38" s="24"/>
       <c r="AT38" s="19" t="s">
@@ -5586,7 +5589,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="39" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="20" t="s">
         <v>49</v>
       </c>
@@ -5705,7 +5708,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="40" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="20" t="s">
         <v>49</v>
       </c>
@@ -5812,7 +5815,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="41" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="20" t="s">
         <v>49</v>
       </c>
@@ -5897,29 +5900,29 @@
         <v>631.70000000000005</v>
       </c>
       <c r="AJ41" s="21">
-        <v>0</v>
+        <v>411.6</v>
       </c>
       <c r="AK41" s="21">
         <v>0</v>
       </c>
       <c r="AL41" s="21">
-        <v>0</v>
+        <v>1989.12</v>
       </c>
       <c r="AM41" s="21"/>
       <c r="AN41" s="21">
-        <v>631.70000000000005</v>
+        <v>1043.3</v>
       </c>
       <c r="AO41" s="21">
-        <v>631.70000000000005</v>
+        <v>1043.3</v>
       </c>
       <c r="AP41" s="22">
         <v>5656.24</v>
       </c>
       <c r="AQ41" s="21">
-        <v>8576.5</v>
+        <v>8988.1</v>
       </c>
       <c r="AR41" s="23">
-        <v>2920.26</v>
+        <v>3331.86</v>
       </c>
       <c r="AS41" s="24"/>
       <c r="AT41" s="19" t="s">
@@ -5935,7 +5938,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="42" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="20" t="s">
         <v>49</v>
       </c>
@@ -6026,7 +6029,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="43" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="20" t="s">
         <v>49</v>
       </c>
@@ -6117,7 +6120,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="44" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="20" t="s">
         <v>49</v>
       </c>
@@ -6222,7 +6225,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="45" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="20" t="s">
         <v>49</v>
       </c>
@@ -6296,7 +6299,9 @@
       <c r="AK45" s="21">
         <v>0</v>
       </c>
-      <c r="AL45" s="21"/>
+      <c r="AL45" s="21">
+        <v>2516.13</v>
+      </c>
       <c r="AM45" s="21"/>
       <c r="AN45" s="21">
         <v>1413.39</v>
@@ -6325,7 +6330,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="46" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="20" t="s">
         <v>49</v>
       </c>
@@ -6394,13 +6399,13 @@
         <v>2744.51</v>
       </c>
       <c r="AJ46" s="21">
-        <v>0</v>
+        <v>472.4</v>
       </c>
       <c r="AK46" s="21">
-        <v>472.4</v>
+        <v>0</v>
       </c>
       <c r="AL46" s="21">
-        <v>0</v>
+        <v>2072.67</v>
       </c>
       <c r="AM46" s="21"/>
       <c r="AN46" s="21">
@@ -6430,7 +6435,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="47" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="20" t="s">
         <v>49</v>
       </c>
@@ -6523,7 +6528,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="48" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="20" t="s">
         <v>49</v>
       </c>
@@ -6614,7 +6619,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="49" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="20" t="s">
         <v>49</v>
       </c>
@@ -6709,7 +6714,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="50" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="20" t="s">
         <v>49</v>
       </c>
@@ -6793,7 +6798,7 @@
       <c r="AG50" s="21"/>
       <c r="AH50" s="21"/>
       <c r="AI50" s="21">
-        <v>2947.01</v>
+        <v>3952.78</v>
       </c>
       <c r="AJ50" s="21">
         <v>0</v>
@@ -6802,25 +6807,25 @@
         <v>0</v>
       </c>
       <c r="AL50" s="21">
-        <v>1220.02</v>
+        <v>117.72</v>
       </c>
       <c r="AM50" s="21">
         <v>4746.0200000000004</v>
       </c>
       <c r="AN50" s="21">
-        <v>2947.01</v>
+        <v>3952.78</v>
       </c>
       <c r="AO50" s="21">
-        <v>-1799.01</v>
+        <v>-793.24</v>
       </c>
       <c r="AP50" s="22">
         <v>18099.88</v>
       </c>
       <c r="AQ50" s="21">
-        <v>14756.51</v>
+        <v>15762.28</v>
       </c>
       <c r="AR50" s="23">
-        <v>-3343.37</v>
+        <v>-2337.6</v>
       </c>
       <c r="AS50" s="24"/>
       <c r="AT50" s="19" t="s">
@@ -6836,7 +6841,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="51" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="20" t="s">
         <v>49</v>
       </c>
@@ -6929,7 +6934,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="52" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="20" t="s">
         <v>49</v>
       </c>
@@ -7018,7 +7023,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="53" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="20" t="s">
         <v>49</v>
       </c>
@@ -7143,7 +7148,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="54" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="20" t="s">
         <v>49</v>
       </c>
@@ -7246,7 +7251,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="55" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="20" t="s">
         <v>49</v>
       </c>
@@ -7369,7 +7374,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="56" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="20" t="s">
         <v>49</v>
       </c>
@@ -7453,7 +7458,9 @@
       <c r="AK56" s="21">
         <v>0</v>
       </c>
-      <c r="AL56" s="21"/>
+      <c r="AL56" s="21">
+        <v>871.41</v>
+      </c>
       <c r="AM56" s="21">
         <v>4820.32</v>
       </c>
@@ -7486,7 +7493,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="57" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="20" t="s">
         <v>49</v>
       </c>
@@ -7611,7 +7618,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="58" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="20" t="s">
         <v>49</v>
       </c>
@@ -7697,13 +7704,13 @@
       <c r="AG58" s="21"/>
       <c r="AH58" s="21"/>
       <c r="AI58" s="21">
-        <v>2333.15</v>
+        <v>2379.6999999999998</v>
       </c>
       <c r="AJ58" s="21">
         <v>0</v>
       </c>
       <c r="AK58" s="21">
-        <v>107.27</v>
+        <v>60.72</v>
       </c>
       <c r="AL58" s="21"/>
       <c r="AM58" s="21">
@@ -7738,7 +7745,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="59" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="20" t="s">
         <v>49</v>
       </c>
@@ -7865,7 +7872,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="60" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="20" t="s">
         <v>49</v>
       </c>
@@ -7949,7 +7956,7 @@
       <c r="AG60" s="21"/>
       <c r="AH60" s="21"/>
       <c r="AI60" s="21">
-        <v>725.37</v>
+        <v>2553.0100000000002</v>
       </c>
       <c r="AJ60" s="21">
         <v>0</v>
@@ -7958,25 +7965,25 @@
         <v>0</v>
       </c>
       <c r="AL60" s="21">
-        <v>1827.64</v>
+        <v>0</v>
       </c>
       <c r="AM60" s="21">
         <v>2672.45</v>
       </c>
       <c r="AN60" s="21">
-        <v>725.37</v>
+        <v>2553.0100000000002</v>
       </c>
       <c r="AO60" s="21">
-        <v>-1947.08</v>
+        <v>-119.44</v>
       </c>
       <c r="AP60" s="22">
         <v>6975.62</v>
       </c>
       <c r="AQ60" s="21">
-        <v>3491.96</v>
+        <v>5319.6</v>
       </c>
       <c r="AR60" s="23">
-        <v>-3483.66</v>
+        <v>-1656.02</v>
       </c>
       <c r="AS60" s="24"/>
       <c r="AT60" s="19" t="s">
@@ -7992,7 +7999,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="61" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="20" t="s">
         <v>49</v>
       </c>
@@ -8093,7 +8100,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="62" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="20" t="s">
         <v>49</v>
       </c>
@@ -8179,10 +8186,10 @@
       <c r="AG62" s="21"/>
       <c r="AH62" s="21"/>
       <c r="AI62" s="21">
-        <v>170.58</v>
+        <v>269.98</v>
       </c>
       <c r="AJ62" s="21">
-        <v>99.4</v>
+        <v>0</v>
       </c>
       <c r="AK62" s="21">
         <v>0</v>
@@ -8220,7 +8227,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="63" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="20" t="s">
         <v>49</v>
       </c>
@@ -8343,7 +8350,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="64" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="20" t="s">
         <v>49</v>
       </c>
@@ -8424,29 +8431,31 @@
       <c r="AH64" s="21"/>
       <c r="AI64" s="21"/>
       <c r="AJ64" s="21">
-        <v>0</v>
+        <v>203.93</v>
       </c>
       <c r="AK64" s="21">
         <v>0</v>
       </c>
-      <c r="AL64" s="21"/>
+      <c r="AL64" s="21">
+        <v>499.89</v>
+      </c>
       <c r="AM64" s="21">
         <v>3148.34</v>
       </c>
       <c r="AN64" s="21">
-        <v>0</v>
+        <v>203.93</v>
       </c>
       <c r="AO64" s="21">
-        <v>-3148.34</v>
+        <v>-2944.41</v>
       </c>
       <c r="AP64" s="22">
         <v>5190.2700000000004</v>
       </c>
       <c r="AQ64" s="21">
-        <v>4068.14</v>
+        <v>4272.07</v>
       </c>
       <c r="AR64" s="23">
-        <v>-1122.1300000000001</v>
+        <v>-918.2</v>
       </c>
       <c r="AS64" s="24"/>
       <c r="AT64" s="19" t="s">
@@ -8462,7 +8471,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="65" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="20" t="s">
         <v>49</v>
       </c>
@@ -8589,7 +8598,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="66" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="20" t="s">
         <v>49</v>
       </c>
@@ -8718,7 +8727,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="67" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="20" t="s">
         <v>49</v>
       </c>
@@ -8807,7 +8816,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="68" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="20" t="s">
         <v>49</v>
       </c>
@@ -8924,7 +8933,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="69" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="20" t="s">
         <v>49</v>
       </c>
@@ -9043,7 +9052,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="70" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="20" t="s">
         <v>49</v>
       </c>
@@ -9140,7 +9149,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="71" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="20" t="s">
         <v>49</v>
       </c>
@@ -9245,7 +9254,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="72" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="20" t="s">
         <v>49</v>
       </c>
@@ -9352,7 +9361,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="73" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="20" t="s">
         <v>49</v>
       </c>
@@ -9455,7 +9464,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="74" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="20" t="s">
         <v>49</v>
       </c>
@@ -9562,7 +9571,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="75" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="20" t="s">
         <v>49</v>
       </c>
@@ -9685,7 +9694,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="76" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="20" t="s">
         <v>49</v>
       </c>
@@ -9774,7 +9783,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="77" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="20" t="s">
         <v>49</v>
       </c>
@@ -9875,7 +9884,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="78" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="20" t="s">
         <v>49</v>
       </c>
@@ -9996,7 +10005,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="79" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="20" t="s">
         <v>49</v>
       </c>
@@ -10103,7 +10112,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="80" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="20" t="s">
         <v>49</v>
       </c>
@@ -10206,7 +10215,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="81" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="20" t="s">
         <v>49</v>
       </c>
@@ -10286,13 +10295,13 @@
       <c r="AG81" s="21"/>
       <c r="AH81" s="21"/>
       <c r="AI81" s="21">
-        <v>961.77</v>
+        <v>1566.63</v>
       </c>
       <c r="AJ81" s="21">
-        <v>422.82</v>
+        <v>0</v>
       </c>
       <c r="AK81" s="21">
-        <v>182.04</v>
+        <v>0</v>
       </c>
       <c r="AL81" s="21">
         <v>0</v>
@@ -10329,7 +10338,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="82" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="20" t="s">
         <v>49</v>
       </c>
@@ -10440,7 +10449,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="83" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="20" t="s">
         <v>49</v>
       </c>
@@ -10537,7 +10546,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="84" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="20" t="s">
         <v>49</v>
       </c>
@@ -10654,7 +10663,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="85" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="20" t="s">
         <v>49</v>
       </c>
@@ -10779,7 +10788,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="86" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="20" t="s">
         <v>49</v>
       </c>
@@ -10854,29 +10863,29 @@
       <c r="AH86" s="21"/>
       <c r="AI86" s="21"/>
       <c r="AJ86" s="21">
-        <v>0</v>
+        <v>68.33</v>
       </c>
       <c r="AK86" s="21">
         <v>0</v>
       </c>
       <c r="AL86" s="21">
-        <v>2011.13</v>
+        <v>1942.8</v>
       </c>
       <c r="AM86" s="21"/>
       <c r="AN86" s="21">
-        <v>0</v>
+        <v>68.33</v>
       </c>
       <c r="AO86" s="21">
-        <v>0</v>
+        <v>68.33</v>
       </c>
       <c r="AP86" s="22">
         <v>2557.86</v>
       </c>
       <c r="AQ86" s="21">
-        <v>1344.94</v>
+        <v>1413.27</v>
       </c>
       <c r="AR86" s="23">
-        <v>-1212.92</v>
+        <v>-1144.5899999999999</v>
       </c>
       <c r="AS86" s="24"/>
       <c r="AT86" s="19" t="s">
@@ -10892,7 +10901,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="87" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="20" t="s">
         <v>49</v>
       </c>
@@ -10972,10 +10981,10 @@
       <c r="AG87" s="21"/>
       <c r="AH87" s="21"/>
       <c r="AI87" s="21">
-        <v>2102.65</v>
+        <v>2505.5100000000002</v>
       </c>
       <c r="AJ87" s="21">
-        <v>402.86</v>
+        <v>0</v>
       </c>
       <c r="AK87" s="21">
         <v>0</v>
@@ -11015,7 +11024,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="88" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="20" t="s">
         <v>49</v>
       </c>
@@ -11116,7 +11125,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="89" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="20" t="s">
         <v>49</v>
       </c>
@@ -11209,7 +11218,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="90" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="20" t="s">
         <v>49</v>
       </c>
@@ -11306,7 +11315,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="91" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="20" t="s">
         <v>49</v>
       </c>
@@ -11391,7 +11400,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="92" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="20" t="s">
         <v>49</v>
       </c>
@@ -11510,7 +11519,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="93" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="20" t="s">
         <v>49</v>
       </c>
@@ -11623,7 +11632,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="94" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="20" t="s">
         <v>49</v>
       </c>
@@ -11746,7 +11755,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="95" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="20" t="s">
         <v>49</v>
       </c>
@@ -11833,7 +11842,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="96" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="20" t="s">
         <v>49</v>
       </c>
@@ -11938,7 +11947,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="97" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="20" t="s">
         <v>49</v>
       </c>
@@ -12041,7 +12050,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="98" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="20" t="s">
         <v>49</v>
       </c>
@@ -12130,7 +12139,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="99" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="20" t="s">
         <v>49</v>
       </c>
@@ -12215,7 +12224,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="100" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="20" t="s">
         <v>49</v>
       </c>
@@ -12342,7 +12351,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="101" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="20" t="s">
         <v>49</v>
       </c>
@@ -12427,7 +12436,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="102" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="20" t="s">
         <v>49</v>
       </c>
@@ -12550,7 +12559,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="103" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="20" t="s">
         <v>49</v>
       </c>
@@ -12645,7 +12654,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="104" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="20" t="s">
         <v>49</v>
       </c>
@@ -12730,7 +12739,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="105" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="20" t="s">
         <v>49</v>
       </c>
@@ -12823,7 +12832,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="106" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="20" t="s">
         <v>49</v>
       </c>
@@ -12952,7 +12961,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="107" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="20" t="s">
         <v>49</v>
       </c>
@@ -13043,7 +13052,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="108" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="20" t="s">
         <v>49</v>
       </c>
@@ -13148,7 +13157,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="109" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="20" t="s">
         <v>49</v>
       </c>
@@ -13271,7 +13280,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="110" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="20" t="s">
         <v>49</v>
       </c>
@@ -13366,7 +13375,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="111" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="20" t="s">
         <v>49</v>
       </c>
@@ -13489,7 +13498,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="112" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="20" t="s">
         <v>49</v>
       </c>
@@ -13578,7 +13587,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="113" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="20" t="s">
         <v>49</v>
       </c>
@@ -13703,7 +13712,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="114" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="20" t="s">
         <v>49</v>
       </c>
@@ -13778,7 +13787,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="115" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="20" t="s">
         <v>280</v>
       </c>
@@ -13867,7 +13876,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="116" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:49" s="19" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="20" t="s">
         <v>280</v>
       </c>
@@ -13963,7 +13972,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:AO116" xr:uid="{9DD1AA80-B25D-432D-986A-8039B0E1D075}"/>
+  <autoFilter ref="A4:AO116" xr:uid="{AF940CA3-7230-4574-93CE-C32F98188DB4}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="8" scale="22" orientation="portrait" verticalDpi="598" r:id="rId1"/>
 </worksheet>

--- a/data/rolling.xlsx
+++ b/data/rolling.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\ugfit022\VOL4\MYSALES\Cubaiu-L\SALES_CONTROLLING\GIORNALIERI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{168E3447-76BC-48BC-9C97-8E1BB1ACB22D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B868DEEB-57C8-499B-A5B4-5ED38F7EC0B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21240" xr2:uid="{A1F4DC9A-275B-4C29-9993-5E29BA996321}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21240" xr2:uid="{AA809ACA-A8B3-4B99-B1E6-9ADAB2211029}"/>
   </bookViews>
   <sheets>
     <sheet name="REPORT" sheetId="1" r:id="rId1"/>
@@ -129,10 +129,10 @@
     <t>GTO Dic'26</t>
   </si>
   <si>
-    <t>MESE: Consegnato al 06/05/2026</t>
-  </si>
-  <si>
-    <t>MESE: In preparazione a magazzino al 06/05/2026</t>
+    <t>MESE: Consegnato al 07/05/2026</t>
+  </si>
+  <si>
+    <t>MESE: In preparazione a magazzino al 07/05/2026</t>
   </si>
   <si>
     <t>Da spedire nel mese di maggio 2026</t>
@@ -1174,13 +1174,13 @@
     </xf>
   </cellXfs>
   <cellStyles count="7">
-    <cellStyle name="Migliaia 2" xfId="4" xr:uid="{5A870D74-AB33-4E05-A832-C3CB62B25762}"/>
+    <cellStyle name="Migliaia 2" xfId="4" xr:uid="{E1FD0D33-E01C-4266-AC58-7C9484539DE1}"/>
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
-    <cellStyle name="Normale 20" xfId="1" xr:uid="{F8CE3CB3-4119-4418-B56B-2A485EDB015C}"/>
-    <cellStyle name="Normale 21" xfId="2" xr:uid="{482A7733-EA90-44B7-800C-6A84CDFC5556}"/>
-    <cellStyle name="Normale 22" xfId="3" xr:uid="{D57BA062-DC77-4548-9897-8FC2D730CB93}"/>
-    <cellStyle name="SAPDataCell" xfId="6" xr:uid="{0E5F5240-E717-44FA-8652-F1AEED32FEE1}"/>
-    <cellStyle name="SAPMemberCell" xfId="5" xr:uid="{4687768F-DF2D-495F-B250-50E4041EDD2B}"/>
+    <cellStyle name="Normale 20" xfId="1" xr:uid="{5D47AEF2-4887-4850-AE15-15DE0EABE0D3}"/>
+    <cellStyle name="Normale 21" xfId="2" xr:uid="{C3198A64-B343-48F7-8506-A509F8AC9967}"/>
+    <cellStyle name="Normale 22" xfId="3" xr:uid="{14E304A0-0197-4229-A11A-26C64863FBD6}"/>
+    <cellStyle name="SAPDataCell" xfId="6" xr:uid="{8F62312F-739E-4D53-82B6-46B1B083D2BA}"/>
+    <cellStyle name="SAPMemberCell" xfId="5" xr:uid="{F5C6E90F-BED4-49F8-AA0C-FB5612F44FC7}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1511,7 +1511,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB7C56AA-4898-4FE6-BC3D-123B7227609C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF7A7656-B4A9-49B6-BA91-FBAE933EE930}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -1545,9 +1545,10 @@
     <col min="43" max="43" width="29.42578125" bestFit="1" customWidth="1"/>
     <col min="44" max="44" width="43.28515625" bestFit="1" customWidth="1"/>
     <col min="45" max="45" width="2.28515625" customWidth="1"/>
-    <col min="46" max="47" width="22.42578125" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="23.42578125" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="22.5703125" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="23.5703125" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="22.85546875" bestFit="1" customWidth="1"/>
     <col min="50" max="50" width="11.5703125" bestFit="1" customWidth="1"/>
     <col min="51" max="51" width="27.7109375" bestFit="1" customWidth="1"/>
     <col min="52" max="52" width="28.7109375" bestFit="1" customWidth="1"/>
@@ -1580,7 +1581,7 @@
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="4">
-        <v>46178</v>
+        <v>46208</v>
       </c>
       <c r="AE2" s="2"/>
       <c r="AH2" s="2"/>
@@ -1851,15 +1852,15 @@
       </c>
       <c r="AI4" s="16">
         <f>SUBTOTAL(9,AI5:AI63748)</f>
-        <v>11309.779999999999</v>
+        <v>18687.740000000002</v>
       </c>
       <c r="AJ4" s="16">
         <f>SUBTOTAL(9,AJ5:AJ63748)</f>
-        <v>3787.9000000000005</v>
+        <v>3314.13</v>
       </c>
       <c r="AK4" s="16">
         <f>SUBTOTAL(9,AK5:AK63748)</f>
-        <v>22667.679999999997</v>
+        <v>19689.440000000006</v>
       </c>
       <c r="AL4" s="16">
         <f>SUBTOTAL(9,AL5:AL63748)</f>
@@ -1871,11 +1872,11 @@
       </c>
       <c r="AN4" s="16">
         <f>SUBTOTAL(9,AN5:AN63748)</f>
-        <v>37765.360000000008</v>
+        <v>41691.310000000012</v>
       </c>
       <c r="AO4" s="16">
         <f>SUBTOTAL(9,AO5:AO63748)</f>
-        <v>-71478.260000000009</v>
+        <v>-67552.310000000027</v>
       </c>
       <c r="AP4" s="16">
         <f>SUBTOTAL(9,AP5:AP63748)</f>
@@ -1883,11 +1884,11 @@
       </c>
       <c r="AQ4" s="16">
         <f>SUBTOTAL(9,AQ5:AQ63748)</f>
-        <v>525804.79000000015</v>
+        <v>529730.74000000022</v>
       </c>
       <c r="AR4" s="16">
         <f>SUBTOTAL(9,AR5:AR63748)</f>
-        <v>-18527.849999999999</v>
+        <v>-14601.899999999996</v>
       </c>
       <c r="AS4" s="16"/>
       <c r="AT4" s="17" t="s">
@@ -4497,9 +4498,11 @@
       <c r="AF28" s="21"/>
       <c r="AG28" s="21"/>
       <c r="AH28" s="21"/>
-      <c r="AI28" s="21"/>
+      <c r="AI28" s="21">
+        <v>136.13</v>
+      </c>
       <c r="AJ28" s="21">
-        <v>136.13</v>
+        <v>0</v>
       </c>
       <c r="AK28" s="21">
         <v>0</v>
@@ -4730,32 +4733,32 @@
       <c r="AG30" s="21"/>
       <c r="AH30" s="21"/>
       <c r="AI30" s="21">
-        <v>171.96</v>
+        <v>495.85</v>
       </c>
       <c r="AJ30" s="21">
-        <v>62.85</v>
+        <v>0</v>
       </c>
       <c r="AK30" s="21">
-        <v>219.93</v>
+        <v>167.46</v>
       </c>
       <c r="AL30" s="21"/>
       <c r="AM30" s="21">
         <v>616.28</v>
       </c>
       <c r="AN30" s="21">
-        <v>454.74</v>
+        <v>663.31</v>
       </c>
       <c r="AO30" s="21">
-        <v>-161.54</v>
+        <v>47.03</v>
       </c>
       <c r="AP30" s="22">
         <v>4389</v>
       </c>
       <c r="AQ30" s="21">
-        <v>3756.56</v>
+        <v>3965.13</v>
       </c>
       <c r="AR30" s="23">
-        <v>-632.44000000000005</v>
+        <v>-423.87</v>
       </c>
       <c r="AS30" s="24"/>
       <c r="AT30" s="19" t="s">
@@ -5141,12 +5144,14 @@
       <c r="AF34" s="21"/>
       <c r="AG34" s="21"/>
       <c r="AH34" s="21"/>
-      <c r="AI34" s="21"/>
+      <c r="AI34" s="21">
+        <v>900.61</v>
+      </c>
       <c r="AJ34" s="21">
         <v>0</v>
       </c>
       <c r="AK34" s="21">
-        <v>2594.2199999999998</v>
+        <v>271.61</v>
       </c>
       <c r="AL34" s="21">
         <v>0</v>
@@ -5155,19 +5160,19 @@
         <v>1537.33</v>
       </c>
       <c r="AN34" s="21">
-        <v>2594.2199999999998</v>
+        <v>1172.22</v>
       </c>
       <c r="AO34" s="21">
-        <v>1056.8900000000001</v>
+        <v>-365.11</v>
       </c>
       <c r="AP34" s="22">
         <v>10573.38</v>
       </c>
       <c r="AQ34" s="21">
-        <v>9489.92</v>
+        <v>8067.92</v>
       </c>
       <c r="AR34" s="23">
-        <v>-1083.46</v>
+        <v>-2505.46</v>
       </c>
       <c r="AS34" s="24"/>
       <c r="AT34" s="19" t="s">
@@ -5551,9 +5556,11 @@
       <c r="AF38" s="21"/>
       <c r="AG38" s="21"/>
       <c r="AH38" s="21"/>
-      <c r="AI38" s="21"/>
+      <c r="AI38" s="21">
+        <v>351.36</v>
+      </c>
       <c r="AJ38" s="21">
-        <v>351.36</v>
+        <v>0</v>
       </c>
       <c r="AK38" s="21">
         <v>669.13</v>
@@ -5903,7 +5910,7 @@
       <c r="AG41" s="21"/>
       <c r="AH41" s="21"/>
       <c r="AI41" s="21">
-        <v>1066.5999999999999</v>
+        <v>2523.9</v>
       </c>
       <c r="AJ41" s="21">
         <v>0</v>
@@ -5918,19 +5925,19 @@
         <v>3069.24</v>
       </c>
       <c r="AN41" s="21">
-        <v>1598.42</v>
+        <v>3055.72</v>
       </c>
       <c r="AO41" s="21">
-        <v>-1470.82</v>
+        <v>-13.52</v>
       </c>
       <c r="AP41" s="22">
         <v>8725.48</v>
       </c>
       <c r="AQ41" s="21">
-        <v>10174.92</v>
+        <v>11632.22</v>
       </c>
       <c r="AR41" s="23">
-        <v>1449.44</v>
+        <v>2906.74</v>
       </c>
       <c r="AS41" s="24"/>
       <c r="AT41" s="19" t="s">
@@ -6302,27 +6309,29 @@
       <c r="AF45" s="21"/>
       <c r="AG45" s="21"/>
       <c r="AH45" s="21"/>
-      <c r="AI45" s="21"/>
+      <c r="AI45" s="21">
+        <v>1359.96</v>
+      </c>
       <c r="AJ45" s="21">
-        <v>1359.96</v>
+        <v>411.98</v>
       </c>
       <c r="AK45" s="21">
-        <v>1156.17</v>
+        <v>0</v>
       </c>
       <c r="AL45" s="21"/>
       <c r="AM45" s="21"/>
       <c r="AN45" s="21">
-        <v>2516.13</v>
+        <v>1771.94</v>
       </c>
       <c r="AO45" s="21">
-        <v>2516.13</v>
+        <v>1771.94</v>
       </c>
       <c r="AP45" s="22"/>
       <c r="AQ45" s="21">
-        <v>10187.56</v>
+        <v>9443.3700000000008</v>
       </c>
       <c r="AR45" s="23">
-        <v>10187.56</v>
+        <v>9443.3700000000008</v>
       </c>
       <c r="AS45" s="24"/>
       <c r="AT45" s="19" t="s">
@@ -6406,30 +6415,30 @@
       <c r="AG46" s="21"/>
       <c r="AH46" s="21"/>
       <c r="AI46" s="21">
-        <v>472.4</v>
+        <v>1554.79</v>
       </c>
       <c r="AJ46" s="21">
-        <v>1082.3900000000001</v>
+        <v>522.28</v>
       </c>
       <c r="AK46" s="21">
-        <v>990.28</v>
+        <v>0</v>
       </c>
       <c r="AL46" s="21">
         <v>0</v>
       </c>
       <c r="AM46" s="21"/>
       <c r="AN46" s="21">
-        <v>2545.0700000000002</v>
+        <v>2077.0700000000002</v>
       </c>
       <c r="AO46" s="21">
-        <v>2545.0700000000002</v>
+        <v>2077.0700000000002</v>
       </c>
       <c r="AP46" s="22"/>
       <c r="AQ46" s="21">
-        <v>15633.97</v>
+        <v>15165.97</v>
       </c>
       <c r="AR46" s="23">
-        <v>15633.97</v>
+        <v>15165.97</v>
       </c>
       <c r="AS46" s="24"/>
       <c r="AT46" s="19" t="s">
@@ -6809,7 +6818,9 @@
       <c r="AF50" s="21"/>
       <c r="AG50" s="21"/>
       <c r="AH50" s="21"/>
-      <c r="AI50" s="21"/>
+      <c r="AI50" s="21">
+        <v>157.46</v>
+      </c>
       <c r="AJ50" s="21">
         <v>0</v>
       </c>
@@ -6823,19 +6834,19 @@
         <v>3014.62</v>
       </c>
       <c r="AN50" s="21">
-        <v>117.72</v>
+        <v>275.18</v>
       </c>
       <c r="AO50" s="21">
-        <v>-2896.9</v>
+        <v>-2739.44</v>
       </c>
       <c r="AP50" s="22">
         <v>21114.5</v>
       </c>
       <c r="AQ50" s="21">
-        <v>15880</v>
+        <v>16037.46</v>
       </c>
       <c r="AR50" s="23">
-        <v>-5234.5</v>
+        <v>-5077.04</v>
       </c>
       <c r="AS50" s="24"/>
       <c r="AT50" s="19" t="s">
@@ -7466,10 +7477,10 @@
       <c r="AG56" s="21"/>
       <c r="AH56" s="21"/>
       <c r="AI56" s="21">
-        <v>551.16999999999996</v>
+        <v>871.41</v>
       </c>
       <c r="AJ56" s="21">
-        <v>320.24</v>
+        <v>0</v>
       </c>
       <c r="AK56" s="21">
         <v>0</v>
@@ -7849,7 +7860,7 @@
         <v>0</v>
       </c>
       <c r="AK59" s="21">
-        <v>2884.57</v>
+        <v>5936.93</v>
       </c>
       <c r="AL59" s="21">
         <v>0</v>
@@ -7858,19 +7869,19 @@
         <v>12958.72</v>
       </c>
       <c r="AN59" s="21">
-        <v>2884.57</v>
+        <v>5936.93</v>
       </c>
       <c r="AO59" s="21">
-        <v>-10074.15</v>
+        <v>-7021.79</v>
       </c>
       <c r="AP59" s="22">
         <v>58205.21</v>
       </c>
       <c r="AQ59" s="21">
-        <v>45823.199999999997</v>
+        <v>48875.56</v>
       </c>
       <c r="AR59" s="23">
-        <v>-12382.01</v>
+        <v>-9329.65</v>
       </c>
       <c r="AS59" s="24"/>
       <c r="AT59" s="19" t="s">
@@ -8206,26 +8217,26 @@
         <v>0</v>
       </c>
       <c r="AK62" s="21">
-        <v>1148.05</v>
+        <v>915.73</v>
       </c>
       <c r="AL62" s="21"/>
       <c r="AM62" s="21">
         <v>535.82000000000005</v>
       </c>
       <c r="AN62" s="21">
-        <v>1148.05</v>
+        <v>915.73</v>
       </c>
       <c r="AO62" s="21">
-        <v>612.23</v>
+        <v>379.91</v>
       </c>
       <c r="AP62" s="22">
         <v>3149.36</v>
       </c>
       <c r="AQ62" s="21">
-        <v>7812.72</v>
+        <v>7580.4</v>
       </c>
       <c r="AR62" s="23">
-        <v>4663.3599999999997</v>
+        <v>4431.04</v>
       </c>
       <c r="AS62" s="24"/>
       <c r="AT62" s="19" t="s">
@@ -8446,10 +8457,10 @@
       <c r="AG64" s="21"/>
       <c r="AH64" s="21"/>
       <c r="AI64" s="21">
-        <v>320.10000000000002</v>
+        <v>703.82</v>
       </c>
       <c r="AJ64" s="21">
-        <v>383.72</v>
+        <v>0</v>
       </c>
       <c r="AK64" s="21">
         <v>0</v>
@@ -9558,24 +9569,24 @@
         <v>0</v>
       </c>
       <c r="AK74" s="21">
-        <v>0</v>
+        <v>796.2</v>
       </c>
       <c r="AL74" s="21"/>
       <c r="AM74" s="21"/>
       <c r="AN74" s="21">
-        <v>0</v>
+        <v>796.2</v>
       </c>
       <c r="AO74" s="21">
-        <v>0</v>
+        <v>796.2</v>
       </c>
       <c r="AP74" s="22">
         <v>1656.35</v>
       </c>
       <c r="AQ74" s="21">
-        <v>1118.94</v>
+        <v>1915.14</v>
       </c>
       <c r="AR74" s="23">
-        <v>-537.41</v>
+        <v>258.79000000000002</v>
       </c>
       <c r="AS74" s="24"/>
       <c r="AT74" s="19" t="s">
@@ -10647,9 +10658,11 @@
       <c r="AF84" s="21"/>
       <c r="AG84" s="21"/>
       <c r="AH84" s="21"/>
-      <c r="AI84" s="21"/>
+      <c r="AI84" s="21">
+        <v>71.099999999999994</v>
+      </c>
       <c r="AJ84" s="21">
-        <v>71.099999999999994</v>
+        <v>0</v>
       </c>
       <c r="AK84" s="21">
         <v>0</v>
@@ -10889,10 +10902,10 @@
         <v>277.05</v>
       </c>
       <c r="AJ86" s="21">
-        <v>0</v>
+        <v>1734.08</v>
       </c>
       <c r="AK86" s="21">
-        <v>1734.08</v>
+        <v>0</v>
       </c>
       <c r="AL86" s="21">
         <v>0</v>
@@ -11743,9 +11756,11 @@
       <c r="AF94" s="21"/>
       <c r="AG94" s="21"/>
       <c r="AH94" s="21"/>
-      <c r="AI94" s="21"/>
+      <c r="AI94" s="21">
+        <v>625.41</v>
+      </c>
       <c r="AJ94" s="21">
-        <v>0</v>
+        <v>645.79</v>
       </c>
       <c r="AK94" s="21">
         <v>0</v>
@@ -11757,19 +11772,19 @@
         <v>4649.09</v>
       </c>
       <c r="AN94" s="21">
-        <v>0</v>
+        <v>1271.2</v>
       </c>
       <c r="AO94" s="21">
-        <v>-4649.09</v>
+        <v>-3377.89</v>
       </c>
       <c r="AP94" s="22">
         <v>12989.03</v>
       </c>
       <c r="AQ94" s="21">
-        <v>6752.07</v>
+        <v>8023.27</v>
       </c>
       <c r="AR94" s="23">
-        <v>-6236.96</v>
+        <v>-4965.76</v>
       </c>
       <c r="AS94" s="24"/>
       <c r="AT94" s="19" t="s">
@@ -12338,13 +12353,13 @@
       <c r="AG100" s="21"/>
       <c r="AH100" s="21"/>
       <c r="AI100" s="21">
-        <v>1327.37</v>
+        <v>1515.61</v>
       </c>
       <c r="AJ100" s="21">
         <v>0</v>
       </c>
       <c r="AK100" s="21">
-        <v>3016.36</v>
+        <v>2999.35</v>
       </c>
       <c r="AL100" s="21">
         <v>0</v>
@@ -12353,19 +12368,19 @@
         <v>2966.21</v>
       </c>
       <c r="AN100" s="21">
-        <v>4343.7299999999996</v>
+        <v>4514.96</v>
       </c>
       <c r="AO100" s="21">
-        <v>1377.52</v>
+        <v>1548.75</v>
       </c>
       <c r="AP100" s="22">
         <v>23442.080000000002</v>
       </c>
       <c r="AQ100" s="21">
-        <v>44819.47</v>
+        <v>44990.7</v>
       </c>
       <c r="AR100" s="23">
-        <v>21377.39</v>
+        <v>21548.62</v>
       </c>
       <c r="AS100" s="24"/>
       <c r="AT100" s="19" t="s">
@@ -12954,7 +12969,7 @@
         <v>0</v>
       </c>
       <c r="AK106" s="21">
-        <v>1838.58</v>
+        <v>1641.32</v>
       </c>
       <c r="AL106" s="21">
         <v>0</v>
@@ -12963,19 +12978,19 @@
         <v>1313.06</v>
       </c>
       <c r="AN106" s="21">
-        <v>1838.58</v>
+        <v>1641.32</v>
       </c>
       <c r="AO106" s="21">
-        <v>525.52</v>
+        <v>328.26</v>
       </c>
       <c r="AP106" s="22">
         <v>8297.01</v>
       </c>
       <c r="AQ106" s="21">
-        <v>10068.18</v>
+        <v>9870.92</v>
       </c>
       <c r="AR106" s="23">
-        <v>1771.17</v>
+        <v>1573.91</v>
       </c>
       <c r="AS106" s="24"/>
       <c r="AT106" s="19" t="s">
@@ -13372,24 +13387,24 @@
       <c r="AI110" s="21"/>
       <c r="AJ110" s="21"/>
       <c r="AK110" s="21">
-        <v>767.26</v>
+        <v>642.66</v>
       </c>
       <c r="AL110" s="21"/>
       <c r="AM110" s="21"/>
       <c r="AN110" s="21">
-        <v>767.26</v>
+        <v>642.66</v>
       </c>
       <c r="AO110" s="21">
-        <v>767.26</v>
+        <v>642.66</v>
       </c>
       <c r="AP110" s="22">
         <v>668.64</v>
       </c>
       <c r="AQ110" s="21">
-        <v>767.26</v>
+        <v>642.66</v>
       </c>
       <c r="AR110" s="23">
-        <v>98.62</v>
+        <v>-25.98</v>
       </c>
       <c r="AS110" s="24"/>
       <c r="AT110" s="19" t="s">
@@ -13704,9 +13719,11 @@
       <c r="AF113" s="21"/>
       <c r="AG113" s="21"/>
       <c r="AH113" s="21"/>
-      <c r="AI113" s="21"/>
+      <c r="AI113" s="21">
+        <v>20.149999999999999</v>
+      </c>
       <c r="AJ113" s="21">
-        <v>20.149999999999999</v>
+        <v>0</v>
       </c>
       <c r="AK113" s="21">
         <v>0</v>
@@ -14004,7 +14021,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:AO116" xr:uid="{CB7C56AA-4898-4FE6-BC3D-123B7227609C}"/>
+  <autoFilter ref="A4:AO116" xr:uid="{EF7A7656-B4A9-49B6-BA91-FBAE933EE930}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="8" scale="20" orientation="portrait" verticalDpi="598" r:id="rId1"/>
 </worksheet>
